--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129327685</v>
+        <v>129332974</v>
       </c>
       <c r="B2" t="n">
-        <v>57721</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,20 +712,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582840</v>
+        <v>582929</v>
       </c>
       <c r="R2" t="n">
-        <v>6325853</v>
+        <v>6325896</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,6 +760,11 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,12 +777,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,32 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332974</v>
+        <v>129327685</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,20 +940,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582929</v>
+        <v>582840</v>
       </c>
       <c r="R4" t="n">
-        <v>6325896</v>
+        <v>6325853</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,11 +988,6 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,12 +1000,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R6" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,79 +1214,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R7" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,82 +1323,81 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129332855</v>
+        <v>129322992</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582856</v>
+        <v>582860</v>
       </c>
       <c r="R8" t="n">
-        <v>6325893</v>
+        <v>6325870</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,92 +1424,103 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129322992</v>
+        <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyelund, Nyelund, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582860</v>
+        <v>582856</v>
       </c>
       <c r="R9" t="n">
-        <v>6325870</v>
+        <v>6325893</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,39 +1547,30 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129332974</v>
+        <v>129327685</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,20 +712,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582929</v>
+        <v>582840</v>
       </c>
       <c r="R2" t="n">
-        <v>6325896</v>
+        <v>6325853</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,11 +760,6 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -777,62 +772,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R3" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,13 +869,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,60 +898,64 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129327685</v>
+        <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>57721</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582840</v>
+        <v>582943</v>
       </c>
       <c r="R4" t="n">
-        <v>6325853</v>
+        <v>6325890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,18 +993,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R6" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,78 +1214,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R7" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,81 +1324,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129322992</v>
+        <v>129332855</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nyelund, Nyelund, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582860</v>
+        <v>582856</v>
       </c>
       <c r="R8" t="n">
-        <v>6325870</v>
+        <v>6325893</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,103 +1426,92 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129332855</v>
+        <v>129322992</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582856</v>
+        <v>582860</v>
       </c>
       <c r="R9" t="n">
-        <v>6325893</v>
+        <v>6325870</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,30 +1538,39 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
         <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R6" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,79 +1214,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R7" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,82 +1323,81 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129332855</v>
+        <v>129322992</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582856</v>
+        <v>582860</v>
       </c>
       <c r="R8" t="n">
-        <v>6325893</v>
+        <v>6325870</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,92 +1424,103 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129322992</v>
+        <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyelund, Nyelund, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582860</v>
+        <v>582856</v>
       </c>
       <c r="R9" t="n">
-        <v>6325870</v>
+        <v>6325893</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,39 +1547,30 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
         <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -784,46 +784,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R3" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,17 +873,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,50 +898,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R4" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,13 +983,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R6" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,78 +1214,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R7" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,19 +1324,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -784,50 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R3" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,13 +869,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,46 +898,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R4" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +987,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R6" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,79 +1214,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R7" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,18 +1323,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,42 +1577,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323221</v>
+        <v>129323024</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1621,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582838</v>
+        <v>582915</v>
       </c>
       <c r="R10" t="n">
-        <v>6325881</v>
+        <v>6325851</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,19 +1659,9 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,59 +1676,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129323024</v>
+        <v>129323221</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>57857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1742,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582915</v>
+        <v>582838</v>
       </c>
       <c r="R11" t="n">
-        <v>6325851</v>
+        <v>6325881</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,9 +1765,19 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -784,46 +784,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R3" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,17 +873,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,50 +898,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R4" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,13 +983,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R6" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,78 +1214,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R7" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,19 +1324,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,47 +1577,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323024</v>
+        <v>129323221</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>57857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582915</v>
+        <v>582838</v>
       </c>
       <c r="R10" t="n">
-        <v>6325851</v>
+        <v>6325881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1654,19 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,54 +1681,59 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129323221</v>
+        <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>57857</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582838</v>
+        <v>582915</v>
       </c>
       <c r="R11" t="n">
-        <v>6325881</v>
+        <v>6325851</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,19 +1775,9 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -784,50 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R3" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,13 +869,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,46 +898,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R4" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +987,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R6" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,79 +1214,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R7" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,80 +1323,83 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129322992</v>
+        <v>129332855</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nyelund, Nyelund, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582860</v>
+        <v>582856</v>
       </c>
       <c r="R8" t="n">
-        <v>6325870</v>
+        <v>6325893</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,103 +1426,92 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129332855</v>
+        <v>129322992</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582856</v>
+        <v>582860</v>
       </c>
       <c r="R9" t="n">
-        <v>6325893</v>
+        <v>6325870</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,30 +1538,39 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
         <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>129332855</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R6" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,78 +1214,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R7" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,83 +1324,80 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129332855</v>
+        <v>129322992</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582856</v>
+        <v>582860</v>
       </c>
       <c r="R8" t="n">
-        <v>6325893</v>
+        <v>6325870</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,92 +1424,103 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129322992</v>
+        <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyelund, Nyelund, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582860</v>
+        <v>582856</v>
       </c>
       <c r="R9" t="n">
-        <v>6325870</v>
+        <v>6325893</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,39 +1547,30 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -1577,42 +1577,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323221</v>
+        <v>129323024</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1621,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582838</v>
+        <v>582915</v>
       </c>
       <c r="R10" t="n">
-        <v>6325881</v>
+        <v>6325851</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,19 +1659,9 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,59 +1676,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129323024</v>
+        <v>129323221</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>57857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1742,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582915</v>
+        <v>582838</v>
       </c>
       <c r="R11" t="n">
-        <v>6325851</v>
+        <v>6325881</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,9 +1765,19 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R6" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,79 +1214,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R7" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,18 +1323,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>129323024</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -1577,47 +1577,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323024</v>
+        <v>129323221</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582915</v>
+        <v>582838</v>
       </c>
       <c r="R10" t="n">
-        <v>6325851</v>
+        <v>6325881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1654,19 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,54 +1681,59 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129323221</v>
+        <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>57857</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582838</v>
+        <v>582915</v>
       </c>
       <c r="R11" t="n">
-        <v>6325881</v>
+        <v>6325851</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,19 +1775,9 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -784,46 +784,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R3" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,17 +873,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,50 +898,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R4" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,13 +983,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129327685</v>
+        <v>129332974</v>
       </c>
       <c r="B2" t="n">
-        <v>57721</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,20 +712,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582840</v>
+        <v>582929</v>
       </c>
       <c r="R2" t="n">
-        <v>6325853</v>
+        <v>6325896</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,6 +760,11 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,76 +777,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332885</v>
+        <v>129327685</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>57721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582943</v>
+        <v>582840</v>
       </c>
       <c r="R3" t="n">
-        <v>6325890</v>
+        <v>6325853</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,65 +880,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R4" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +987,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -675,46 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R2" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,17 +764,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -898,50 +898,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332885</v>
+        <v>129332974</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582943</v>
+        <v>582929</v>
       </c>
       <c r="R4" t="n">
-        <v>6325890</v>
+        <v>6325896</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,13 +983,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1577,42 +1577,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323221</v>
+        <v>129323024</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1621,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582838</v>
+        <v>582915</v>
       </c>
       <c r="R10" t="n">
-        <v>6325881</v>
+        <v>6325851</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,19 +1659,9 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,59 +1676,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129323024</v>
+        <v>129323221</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>57857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1742,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582915</v>
+        <v>582838</v>
       </c>
       <c r="R11" t="n">
-        <v>6325851</v>
+        <v>6325881</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,9 +1765,19 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -675,64 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129332885</v>
+        <v>129327685</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>57721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582943</v>
+        <v>582840</v>
       </c>
       <c r="R2" t="n">
-        <v>6325890</v>
+        <v>6325853</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,51 +766,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129327685</v>
+        <v>129332974</v>
       </c>
       <c r="B3" t="n">
-        <v>57721</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,20 +821,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582840</v>
+        <v>582929</v>
       </c>
       <c r="R3" t="n">
-        <v>6325853</v>
+        <v>6325896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,6 +869,11 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög mellan träden över mig</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -886,58 +886,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332974</v>
+        <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582929</v>
+        <v>582943</v>
       </c>
       <c r="R4" t="n">
-        <v>6325896</v>
+        <v>6325890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +987,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög mellan träden över mig</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R6" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,78 +1214,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R7" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,19 +1324,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1577,47 +1577,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323024</v>
+        <v>129323221</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582915</v>
+        <v>582838</v>
       </c>
       <c r="R10" t="n">
-        <v>6325851</v>
+        <v>6325881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,9 +1654,19 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,54 +1681,59 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129323221</v>
+        <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>57857</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582838</v>
+        <v>582915</v>
       </c>
       <c r="R11" t="n">
-        <v>6325881</v>
+        <v>6325851</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,19 +1775,9 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,12 +1792,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 49075-2025 artfynd.xlsx
+++ b/artfynd/A 49075-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129327685</v>
       </c>
       <c r="B2" t="n">
-        <v>57721</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129332974</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129332885</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129324491</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,60 +1123,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129327777</v>
+        <v>129333026</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
+          <t>Nyelund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582964</v>
+        <v>582831</v>
       </c>
       <c r="R6" t="n">
-        <v>6325858</v>
+        <v>6325851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,79 +1214,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129333026</v>
+        <v>129327777</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyelund, Sm</t>
+          <t>Nyelund, Kevershäll, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582831</v>
+        <v>582964</v>
       </c>
       <c r="R7" t="n">
-        <v>6325851</v>
+        <v>6325858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,18 +1323,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1345,7 +1345,7 @@
         <v>129322992</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129332855</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>129323221</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>129323024</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>129327856</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129327745</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>129327832</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>129323339</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
